--- a/涉华投资仲裁案例统计总表（updated 251126）_KeerHuang.xlsx
+++ b/涉华投资仲裁案例统计总表（updated 251126）_KeerHuang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 科研材料\【工作】2024废物上工\Z中心和公众号事宜\【项目】涉华投资仲裁案例实时跟踪\涉华ISDS案件可视化 v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7296B5A2-0A6C-4A84-9DBE-E6E44A4315EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6269AEED-9D66-442E-B2AD-A1BB2971EC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2602" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cases initiated by PRC investor" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="cases against China" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'cases against China'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'cases against China'!$A$1:$R$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'cases initiated by PRC investor'!$N$1:$N$1000</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="450">
   <si>
     <t xml:space="preserve">Number </t>
   </si>
@@ -1181,9 +1181,6 @@
     <t>Claimant-nationality</t>
   </si>
   <si>
-    <t>Ekran Berhad v. People's Republic of China</t>
-  </si>
-  <si>
     <t>ICSID Case No. ARB/11/15</t>
   </si>
   <si>
@@ -1211,9 +1208,6 @@
   </si>
   <si>
     <t>Arts and culture facilities</t>
-  </si>
-  <si>
-    <t>Ansung Housing Co., Ltd. v. China</t>
   </si>
   <si>
     <t>ICSID Case No. ARB/14/25</t>
@@ -1358,9 +1352,6 @@
   </si>
   <si>
     <t>China-United Kingdom BIT (1986)</t>
-  </si>
-  <si>
-    <t>Macro Trading Co., Ltd. v. China</t>
   </si>
   <si>
     <t>ICSID Case No. ARB/20/22</t>
@@ -1582,6 +1573,21 @@
   </si>
   <si>
     <t>Qiong Ye and Jianping Yang v.  Cambodia</t>
+  </si>
+  <si>
+    <t>official link</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>Ekran Berhad v. China</t>
+  </si>
+  <si>
+    <t>Ansung Housing v. China</t>
+  </si>
+  <si>
+    <t>Macro Trading v. China</t>
   </si>
 </sst>
 </file>
@@ -2074,7 +2080,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="13" customFormat="1" ht="200" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>1</v>
@@ -2164,7 +2170,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>25</v>
@@ -2173,7 +2179,7 @@
         <v>26</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>27</v>
@@ -2275,7 +2281,7 @@
       <c r="Z3" s="6"/>
       <c r="AA3" s="6"/>
     </row>
-    <row r="4" spans="1:27" ht="200" hidden="1" customHeight="1">
+    <row r="4" spans="1:27" ht="216.75" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2426,7 +2432,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>38</v>
@@ -2610,7 +2616,7 @@
       <c r="Z8" s="6"/>
       <c r="AA8" s="6"/>
     </row>
-    <row r="9" spans="1:27" ht="200" hidden="1" customHeight="1">
+    <row r="9" spans="1:27" ht="186" customHeight="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2958,7 +2964,7 @@
         <v>169</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>38</v>
@@ -3140,7 +3146,7 @@
       <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
     </row>
-    <row r="17" spans="1:27" ht="200" hidden="1" customHeight="1">
+    <row r="17" spans="1:27" ht="179.25" customHeight="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3340,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>226</v>
@@ -3352,7 +3358,7 @@
         <v>227</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>38</v>
@@ -3407,7 +3413,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C21" s="26" t="s">
         <v>237</v>
@@ -3614,7 +3620,7 @@
         <v>238</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>38</v>
@@ -3679,7 +3685,7 @@
         <v>281</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>38</v>
@@ -3744,7 +3750,7 @@
         <v>281</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>38</v>
@@ -3809,7 +3815,7 @@
         <v>297</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>38</v>
@@ -32446,19 +32452,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C5" s="4">
         <v>2025</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>342</v>
@@ -32654,13 +32660,15 @@
     <col min="11" max="11" width="34.3984375" style="3" customWidth="1"/>
     <col min="12" max="12" width="19.86328125" style="3" customWidth="1"/>
     <col min="13" max="13" width="21" style="3" customWidth="1"/>
-    <col min="14" max="14" width="17.3984375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="22.06640625" style="3" customWidth="1"/>
     <col min="15" max="15" width="22.265625" style="3" customWidth="1"/>
     <col min="16" max="16" width="17.86328125" style="3" customWidth="1"/>
     <col min="17" max="17" width="19" style="3" customWidth="1"/>
     <col min="18" max="18" width="12.73046875" style="3" customWidth="1"/>
     <col min="19" max="19" width="30.73046875" style="3" customWidth="1"/>
-    <col min="20" max="26" width="8.73046875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="20.3984375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="27.46484375" style="3" customWidth="1"/>
+    <col min="22" max="26" width="8.73046875" style="3" customWidth="1"/>
     <col min="27" max="16384" width="14.3984375" style="3"/>
   </cols>
   <sheetData>
@@ -32722,8 +32730,12 @@
       <c r="S1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
+      <c r="T1" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>446</v>
+      </c>
       <c r="V1" s="12"/>
       <c r="W1" s="12"/>
       <c r="X1" s="12"/>
@@ -32735,34 +32747,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="D2" s="4">
         <v>2011</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>135</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>135</v>
@@ -32771,7 +32783,7 @@
         <v>135</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>84</v>
@@ -32780,7 +32792,7 @@
         <v>31</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>111</v>
@@ -32799,43 +32811,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D3" s="4">
         <v>2014</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>364</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>84</v>
@@ -32844,10 +32856,10 @@
         <v>31</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="S3" s="4"/>
       <c r="T3" s="6"/>
@@ -32863,10 +32875,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D4" s="4">
         <v>2017</v>
@@ -32875,31 +32887,31 @@
         <v>124</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>84</v>
@@ -32908,7 +32920,7 @@
         <v>31</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="R4" s="4" t="s">
         <v>133</v>
@@ -32927,7 +32939,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>135</v>
@@ -32939,19 +32951,19 @@
         <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>150</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>150</v>
@@ -32963,7 +32975,7 @@
         <v>150</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>46</v>
@@ -32972,7 +32984,7 @@
         <v>135</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>133</v>
@@ -32991,43 +33003,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D6" s="4">
         <v>2019</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>395</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>150</v>
@@ -33055,10 +33067,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D7" s="4">
         <v>2020</v>
@@ -33067,31 +33079,31 @@
         <v>309</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>183</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>84</v>
@@ -33103,7 +33115,7 @@
         <v>166</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="6"/>
@@ -33119,10 +33131,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8" s="4">
         <v>2020</v>
@@ -33131,31 +33143,31 @@
         <v>309</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>411</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>107</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>84</v>
@@ -33164,10 +33176,10 @@
         <v>31</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="S8" s="4"/>
       <c r="T8" s="6"/>
@@ -33183,10 +33195,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D9" s="4">
         <v>2020</v>
@@ -33195,31 +33207,31 @@
         <v>179</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="M9" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>422</v>
-      </c>
       <c r="N9" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>84</v>
@@ -33228,10 +33240,10 @@
         <v>31</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="S9" s="4"/>
       <c r="T9" s="6"/>
@@ -33247,10 +33259,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D10" s="4">
         <v>2021</v>
@@ -33259,31 +33271,31 @@
         <v>201</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>107</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>46</v>
@@ -33292,7 +33304,7 @@
         <v>47</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>133</v>
@@ -33311,7 +33323,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>135</v>
@@ -33323,19 +33335,19 @@
         <v>201</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>150</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>150</v>
@@ -33347,7 +33359,7 @@
         <v>150</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>46</v>
@@ -61063,7 +61075,7 @@
       <c r="Z1000" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:R11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/涉华投资仲裁案例统计总表（updated 251126）_KeerHuang.xlsx
+++ b/涉华投资仲裁案例统计总表（updated 251126）_KeerHuang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 科研材料\【工作】2024废物上工\Z中心和公众号事宜\【项目】涉华投资仲裁案例实时跟踪\涉华ISDS案件可视化 v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6269AEED-9D66-442E-B2AD-A1BB2971EC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B02560-0C79-44E4-B40D-4EBA09C16CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cases initiated by PRC investor" sheetId="1" r:id="rId1"/>
@@ -32923,7 +32923,7 @@
         <v>375</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>133</v>
+        <v>364</v>
       </c>
       <c r="S4" s="4"/>
       <c r="T4" s="6"/>
